--- a/emisiones.xlsx
+++ b/emisiones.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t xml:space="preserve"> Direct (At Point of Emissions)</t>
   </si>
@@ -64,6 +64,12 @@
   <si>
     <t xml:space="preserve">CC</t>
   </si>
+  <si>
+    <t xml:space="preserve">tend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alt</t>
+  </si>
 </sst>
 </file>
 
@@ -71,8 +77,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="\ * #,##0.00\ ;\-* #,##0.00\ ;\ * \-#\ ;\ @\ "/>
-    <numFmt numFmtId="166" formatCode="\ * #,##0.000\ ;\ * \-#,##0.000\ ;\ * \-#\ ;\ @\ "/>
+    <numFmt numFmtId="165" formatCode="* #,##0.00\ ;\-* #,##0.00\ ;* \-#\ ;@\ "/>
+    <numFmt numFmtId="166" formatCode="* #,##0.000\ ;* \-#,##0.000\ ;* \-#\ ;@\ "/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -80,6 +86,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -262,13 +269,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BA15"/>
-  <sheetFormatPr defaultColWidth="10.6875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="96.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="2" style="0" width="5.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="7.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="26" style="0" width="8.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="32" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="32" style="0" width="9.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1684,8 +1691,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:E30"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:K31"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1715,6 +1722,22 @@
       <c r="E3" s="0" t="n">
         <v>-6.35473902653253</v>
       </c>
+      <c r="F3" s="0" t="n">
+        <f aca="false">SUM(C3:E3)</f>
+        <v>-7.23021275024198</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>-7.51417701236083</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="0" t="n">
@@ -1729,6 +1752,22 @@
       <c r="E4" s="0" t="n">
         <v>-11.3141107282311</v>
       </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">SUM(C4:E4)</f>
+        <v>-13.4020081737106</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>-13.3783537875876</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>-7.23021275024198</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>-7.51417701236083</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="n">
@@ -1743,6 +1782,22 @@
       <c r="E5" s="0" t="n">
         <v>-14.6704008905723</v>
       </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false">SUM(C5:E5)</f>
+        <v>-15.8997687635658</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-28.7611040997717</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>-13.4020081737106</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>-13.3783537875876</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="n">
@@ -1757,6 +1812,22 @@
       <c r="E6" s="0" t="n">
         <v>-26.330164572891</v>
       </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">SUM(C6:E6)</f>
+        <v>-27.0774442987782</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>-44.1616006918474</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>-15.8997687635658</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>-28.7611040997717</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="n">
@@ -1771,6 +1842,22 @@
       <c r="E7" s="0" t="n">
         <v>-41.6041008944185</v>
       </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false">SUM(C7:E7)</f>
+        <v>-42.7732865820055</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>-62.0886729839197</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>-27.0774442987782</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>-44.1616006918474</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="n">
@@ -1785,6 +1872,22 @@
       <c r="E8" s="0" t="n">
         <v>-59.0127297526077</v>
       </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">SUM(C8:E8)</f>
+        <v>-60.6713297682803</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>-66.5170585865966</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>-42.7732865820055</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>-62.0886729839197</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="n">
@@ -1799,6 +1902,22 @@
       <c r="E9" s="0" t="n">
         <v>-78.1194750030457</v>
       </c>
+      <c r="F9" s="0" t="n">
+        <f aca="false">SUM(C9:E9)</f>
+        <v>-80.3151040176745</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>-28.5959281537094</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>-60.6713297682803</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>-66.5170585865966</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="n">
@@ -1813,6 +1932,22 @@
       <c r="E10" s="0" t="n">
         <v>-98.2944745836099</v>
       </c>
+      <c r="F10" s="0" t="n">
+        <f aca="false">SUM(C10:E10)</f>
+        <v>-101.05715778181</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>-7.20115614945153</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>-80.3151040176745</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>-28.5959281537094</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="n">
@@ -1827,6 +1962,22 @@
       <c r="E11" s="0" t="n">
         <v>-118.973555638173</v>
       </c>
+      <c r="F11" s="0" t="n">
+        <f aca="false">SUM(C11:E11)</f>
+        <v>-122.317461124759</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>-6.80485789711028</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>2030</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>-101.05715778181</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>-7.20115614945153</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="n">
@@ -1841,6 +1992,22 @@
       <c r="E12" s="0" t="n">
         <v>-139.563028501536</v>
       </c>
+      <c r="F12" s="0" t="n">
+        <f aca="false">SUM(C12:E12)</f>
+        <v>-143.488285986367</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>-10.2094195203029</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>2031</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>-122.317461124759</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>-6.80485789711028</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="n">
@@ -1855,6 +2022,22 @@
       <c r="E13" s="0" t="n">
         <v>-159.232767395219</v>
       </c>
+      <c r="F13" s="0" t="n">
+        <f aca="false">SUM(C13:E13)</f>
+        <v>-168.443462802924</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>-9.61655132136437</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>2032</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>-143.488285986367</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>-10.2094195203029</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="n">
@@ -1869,6 +2052,22 @@
       <c r="E14" s="0" t="n">
         <v>-179.493300797833</v>
       </c>
+      <c r="F14" s="0" t="n">
+        <f aca="false">SUM(C14:E14)</f>
+        <v>-193.156419099</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>-10.7869815746474</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>2033</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>-168.443462802924</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>-9.61655132136437</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="n">
@@ -1883,6 +2082,22 @@
       <c r="E15" s="0" t="n">
         <v>-201.071798222988</v>
       </c>
+      <c r="F15" s="0" t="n">
+        <f aca="false">SUM(C15:E15)</f>
+        <v>-210.755202245844</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>-11.8915304512061</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>2034</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>-193.156419099</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>-10.7869815746474</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="n">
@@ -1897,6 +2112,22 @@
       <c r="E16" s="0" t="n">
         <v>-214.289908274615</v>
       </c>
+      <c r="F16" s="0" t="n">
+        <f aca="false">SUM(C16:E16)</f>
+        <v>-220.326778837784</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>-13.9987330024754</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>2035</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>-210.755202245844</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <v>-11.8915304512061</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="n">
@@ -1911,6 +2142,22 @@
       <c r="E17" s="0" t="n">
         <v>-220.333748624574</v>
       </c>
+      <c r="F17" s="0" t="n">
+        <f aca="false">SUM(C17:E17)</f>
+        <v>-226.810267359655</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>-21.6041942784363</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>2036</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>-220.326778837784</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>-13.9987330024754</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="n">
@@ -1925,6 +2172,22 @@
       <c r="E18" s="0" t="n">
         <v>-223.54402250193</v>
       </c>
+      <c r="F18" s="0" t="n">
+        <f aca="false">SUM(C18:E18)</f>
+        <v>-248.101376723256</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>-25.7584343276226</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>2037</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>-226.810267359655</v>
+      </c>
+      <c r="K18" s="0" t="n">
+        <v>-21.6041942784363</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="n">
@@ -1939,6 +2202,22 @@
       <c r="E19" s="0" t="n">
         <v>-222.108007140967</v>
       </c>
+      <c r="F19" s="0" t="n">
+        <f aca="false">SUM(C19:E19)</f>
+        <v>-269.09409468111</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>-34.5185971183322</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>2038</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>-248.101376723256</v>
+      </c>
+      <c r="K19" s="0" t="n">
+        <v>-25.7584343276226</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="n">
@@ -1953,6 +2232,22 @@
       <c r="E20" s="0" t="n">
         <v>-214.541742572523</v>
       </c>
+      <c r="F20" s="0" t="n">
+        <f aca="false">SUM(C20:E20)</f>
+        <v>-280.688632695968</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>-42.9758088736659</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>2039</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>-269.09409468111</v>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>-34.5185971183322</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="n">
@@ -1967,6 +2262,22 @@
       <c r="E21" s="0" t="n">
         <v>-198.888109510668</v>
       </c>
+      <c r="F21" s="0" t="n">
+        <f aca="false">SUM(C21:E21)</f>
+        <v>-301.212956473179</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>-45.0360613062279</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>2040</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>-280.688632695968</v>
+      </c>
+      <c r="K21" s="0" t="n">
+        <v>-42.9758088736659</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="n">
@@ -1981,6 +2292,22 @@
       <c r="E22" s="0" t="n">
         <v>-188.836454345604</v>
       </c>
+      <c r="F22" s="0" t="n">
+        <f aca="false">SUM(C22:E22)</f>
+        <v>-353.005072369054</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>-56.3080362467966</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>2041</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>-301.212956473179</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>-45.0360613062279</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="n">
@@ -1995,6 +2322,22 @@
       <c r="E23" s="0" t="n">
         <v>-186.874187379051</v>
       </c>
+      <c r="F23" s="0" t="n">
+        <f aca="false">SUM(C23:E23)</f>
+        <v>-408.470712987139</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>-66.3995309408421</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>2042</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>-353.005072369054</v>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>-56.3080362467966</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="n">
@@ -2009,6 +2352,22 @@
       <c r="E24" s="0" t="n">
         <v>-189.391269873809</v>
       </c>
+      <c r="F24" s="0" t="n">
+        <f aca="false">SUM(C24:E24)</f>
+        <v>-465.271726447735</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>-71.2939580124807</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>2043</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>-408.470712987139</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>-66.3995309408421</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="n">
@@ -2023,6 +2382,22 @@
       <c r="E25" s="0" t="n">
         <v>-195.525319137845</v>
       </c>
+      <c r="F25" s="0" t="n">
+        <f aca="false">SUM(C25:E25)</f>
+        <v>-500.810195750405</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>-75.4901894346291</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>2044</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>-465.271726447735</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>-71.2939580124807</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="n">
@@ -2037,6 +2412,22 @@
       <c r="E26" s="0" t="n">
         <v>-196.204751368544</v>
       </c>
+      <c r="F26" s="0" t="n">
+        <f aca="false">SUM(C26:E26)</f>
+        <v>-538.648722331795</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>-82.9649746541974</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>2045</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>-500.810195750405</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>-75.4901894346291</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="n">
@@ -2051,6 +2442,22 @@
       <c r="E27" s="0" t="n">
         <v>-200.773000486203</v>
       </c>
+      <c r="F27" s="0" t="n">
+        <f aca="false">SUM(C27:E27)</f>
+        <v>-581.963356835201</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>-98.8743362608283</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>2046</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>-538.648722331795</v>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>-82.9649746541974</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="n">
@@ -2065,6 +2472,22 @@
       <c r="E28" s="0" t="n">
         <v>-252.020457742368</v>
       </c>
+      <c r="F28" s="0" t="n">
+        <f aca="false">SUM(C28:E28)</f>
+        <v>-642.98097199666</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>-117.4882302039</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>2047</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>-581.963356835201</v>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>-98.8743362608283</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="n">
@@ -2079,6 +2502,22 @@
       <c r="E29" s="0" t="n">
         <v>-272.151402093188</v>
       </c>
+      <c r="F29" s="0" t="n">
+        <f aca="false">SUM(C29:E29)</f>
+        <v>-718.508155458009</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>-142.564722711842</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>2048</v>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>-642.98097199666</v>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>-117.4882302039</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="n">
@@ -2092,6 +2531,33 @@
       </c>
       <c r="E30" s="0" t="n">
         <v>-303.567035915083</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <f aca="false">SUM(C30:E30)</f>
+        <v>-783.981033075858</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>-150.378911228962</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>2049</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>-718.508155458009</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>-142.564722711842</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="0" t="n">
+        <v>2050</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>-783.981033075858</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>-150.378911228962</v>
       </c>
     </row>
   </sheetData>

--- a/emisiones.xlsx
+++ b/emisiones.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
@@ -269,7 +269,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BA15"/>
-  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.71484375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="96.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="2" style="0" width="5.01"/>
@@ -1692,7 +1692,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:K31"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1763,7 +1763,7 @@
         <v>2023</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>-7.23021275024198</v>
+        <v>-6.6775091447667</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>-7.51417701236083</v>
@@ -1793,7 +1793,7 @@
         <v>2024</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>-13.4020081737106</v>
+        <v>-11.8887377302378</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>-13.3783537875876</v>
@@ -1823,7 +1823,7 @@
         <v>2025</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>-15.8997687635658</v>
+        <v>-25.5586919663816</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>-28.7611040997717</v>
@@ -1853,7 +1853,7 @@
         <v>2026</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>-27.0774442987782</v>
+        <v>-44.9845020773099</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>-44.1616006918474</v>
@@ -1883,7 +1883,7 @@
         <v>2027</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>-42.7732865820055</v>
+        <v>-61.4678672650139</v>
       </c>
       <c r="K8" s="0" t="n">
         <v>-62.0886729839197</v>
@@ -1913,7 +1913,7 @@
         <v>2028</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>-60.6713297682803</v>
+        <v>-88.4370381618262</v>
       </c>
       <c r="K9" s="0" t="n">
         <v>-66.5170585865966</v>
@@ -1943,7 +1943,7 @@
         <v>2029</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>-80.3151040176745</v>
+        <v>-118.269847125193</v>
       </c>
       <c r="K10" s="0" t="n">
         <v>-28.5959281537094</v>
@@ -1973,7 +1973,7 @@
         <v>2030</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>-101.05715778181</v>
+        <v>-150.23098169563</v>
       </c>
       <c r="K11" s="0" t="n">
         <v>-7.20115614945153</v>
@@ -2003,7 +2003,7 @@
         <v>2031</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>-122.317461124759</v>
+        <v>-187.042298347172</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>-6.80485789711028</v>
@@ -2033,7 +2033,7 @@
         <v>2032</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>-143.488285986367</v>
+        <v>-224.3874367735</v>
       </c>
       <c r="K13" s="0" t="n">
         <v>-10.2094195203029</v>
@@ -2063,7 +2063,7 @@
         <v>2033</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>-168.443462802924</v>
+        <v>-260.74232543094</v>
       </c>
       <c r="K14" s="0" t="n">
         <v>-9.61655132136437</v>
@@ -2093,7 +2093,7 @@
         <v>2034</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>-193.156419099</v>
+        <v>-296.197796547421</v>
       </c>
       <c r="K15" s="0" t="n">
         <v>-10.7869815746474</v>
@@ -2123,7 +2123,7 @@
         <v>2035</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>-210.755202245844</v>
+        <v>-334.812808959047</v>
       </c>
       <c r="K16" s="0" t="n">
         <v>-11.8915304512061</v>
@@ -2153,7 +2153,7 @@
         <v>2036</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>-220.326778837784</v>
+        <v>-367.353184438405</v>
       </c>
       <c r="K17" s="0" t="n">
         <v>-13.9987330024754</v>
@@ -2183,7 +2183,7 @@
         <v>2037</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>-226.810267359655</v>
+        <v>-397.608038532294</v>
       </c>
       <c r="K18" s="0" t="n">
         <v>-21.6041942784363</v>
@@ -2213,7 +2213,7 @@
         <v>2038</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>-248.101376723256</v>
+        <v>-421.066755712482</v>
       </c>
       <c r="K19" s="0" t="n">
         <v>-25.7584343276226</v>
@@ -2243,7 +2243,7 @@
         <v>2039</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>-269.09409468111</v>
+        <v>-444.387250509636</v>
       </c>
       <c r="K20" s="0" t="n">
         <v>-34.5185971183322</v>
@@ -2273,7 +2273,7 @@
         <v>2040</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>-280.688632695968</v>
+        <v>-470.716389457874</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>-42.9758088736659</v>
@@ -2303,7 +2303,7 @@
         <v>2041</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>-301.212956473179</v>
+        <v>-498.365419258794</v>
       </c>
       <c r="K22" s="0" t="n">
         <v>-45.0360613062279</v>
@@ -2333,7 +2333,7 @@
         <v>2042</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>-353.005072369054</v>
+        <v>-513.296405157654</v>
       </c>
       <c r="K23" s="0" t="n">
         <v>-56.3080362467966</v>
@@ -2363,7 +2363,7 @@
         <v>2043</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>-408.470712987139</v>
+        <v>-540.285896318535</v>
       </c>
       <c r="K24" s="0" t="n">
         <v>-66.3995309408421</v>
@@ -2393,7 +2393,7 @@
         <v>2044</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>-465.271726447735</v>
+        <v>-576.866243733138</v>
       </c>
       <c r="K25" s="0" t="n">
         <v>-71.2939580124807</v>
@@ -2423,7 +2423,7 @@
         <v>2045</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>-500.810195750405</v>
+        <v>-603.188586764548</v>
       </c>
       <c r="K26" s="0" t="n">
         <v>-75.4901894346291</v>
@@ -2453,7 +2453,7 @@
         <v>2046</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>-538.648722331795</v>
+        <v>-629.345511823816</v>
       </c>
       <c r="K27" s="0" t="n">
         <v>-82.9649746541974</v>
@@ -2483,7 +2483,7 @@
         <v>2047</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>-581.963356835201</v>
+        <v>-601.476561330789</v>
       </c>
       <c r="K28" s="0" t="n">
         <v>-98.8743362608283</v>
@@ -2513,7 +2513,7 @@
         <v>2048</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>-642.98097199666</v>
+        <v>-602.870933790815</v>
       </c>
       <c r="K29" s="0" t="n">
         <v>-117.4882302039</v>
@@ -2543,7 +2543,7 @@
         <v>2049</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>-718.508155458009</v>
+        <v>-661.401878371477</v>
       </c>
       <c r="K30" s="0" t="n">
         <v>-142.564722711842</v>
@@ -2554,7 +2554,7 @@
         <v>2050</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>-783.981033075858</v>
+        <v>-729.007473066787</v>
       </c>
       <c r="K31" s="0" t="n">
         <v>-150.378911228962</v>
